--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00219_18600707.4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00219_18600707.4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.4.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -995,7 +995,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00219_18600707.4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00219_18600707.4" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -609,24 +609,28 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: remÃ©dy all inquirers: moreover, I shall</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: Â¥-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L199: isolated marker/symbol line :: P</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -636,7 +640,7 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: quote/punctuation debris :: unto the third and fourth generation ; indeed, â€”., 171.</t>
+          <t>L136: punctuation artifact: repeated periods :: For any one of the four Reviews ...</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -673,7 +677,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>924</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -696,34 +700,34 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ï¼�</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œthe cosmetics and other toilet</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ¥-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L201: isolated marker/symbol line :: 000</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: Â¥-</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ¥-</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
         <is>
-          <t>L332: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Head Office...â€¦. Church Street. Toronto:</t>
+          <t>L332: punctuation artifact: repeated periods :: Head Office...…. Church Street. Toronto:</t>
         </is>
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L136: punctuation artifact: repeated periods :: For any one of the four Reviews ...</t>
+          <t>L142: punctuation artifact: double/multiple hyphen :: For Blackwood’s Magazine, -------</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -783,19 +787,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L277: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN :: States it wÃ¤re rapidly becoming gray but up</t>
+          <t>L193: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: OUR MUSICAL FRIEND. Scrofula, or Kingâ€™s Evil,</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 • Quarter-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L221: isolated marker/symbol line :: J</t>
+          <t>L193: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -810,13 +814,13 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: For Blackwoodâ€™s Magazine, -------</t>
+          <t>L185: punctuation artifact: repeated periods :: LEONARD SCOTT &amp; Co.. $2.50 each constantly on hand</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________â€” ------------- ----: ---107 Nassau St., New York.</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •Subscribe to . Our Musical Friend," or</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -843,7 +847,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>122</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -866,19 +870,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L332: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Head Office...â€¦. Church Street. Toronto:</t>
+          <t>L377: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00, U+51CF CJK UNIFIED IDEOGRAPH-51CF :: 一 减</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”is a constitutional disease, a corruption of the</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •Subscribe to . Our Musical Friend," or</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L359: isolated marker/symbol line :: b.</t>
+          <t>L199: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -888,24 +892,24 @@
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>L1198: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Head Office...â€¦. Church Street. Toronto:</t>
+          <t>L1198: punctuation artifact: repeated periods :: Head Office...…. Church Street. Toronto:</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L185: punctuation artifact: repeated periods :: LEONARD SCOTT &amp; Co.. $2.50 each constantly on hand</t>
+          <t>L191: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________— ------------- ----: ---107 Nassau St., New York.</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
+          <t>L191: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________— ------------- ----: ---107 Nassau St., New York.</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr">
         <is>
-          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with Â© Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
+          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with © Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
         </is>
       </c>
       <c r="V5" s="1" t="inlineStr"/>
@@ -944,24 +948,24 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 â€¢ Quarter-</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 • Quarter-</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): A1001 (letter/digit mix) :: â€” A1001</t>
+          <t>L561: stray/suspicious non-ASCII glyph(s): U+2265 GREATER-THAN OR EQUAL TO | isolated marker/symbol line :: ≥</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 â€¢ Quarter-</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: it seems to be the rod of Him who says, •• I Both the Ointment and Pills should be</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L360: isolated marker/symbol line :: A</t>
+          <t>L201: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -972,13 +976,13 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________â€” ------------- ----: ---107 Nassau St., New York.</t>
+          <t>L230: punctuation artifact: double/multiple hyphen :: _— ______________- ----------------— The treatment they adopt is the result of</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: _________________________â€” â€” correct detail of their cases witha remit-</t>
+          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr"/>
@@ -1028,19 +1032,19 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L377: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ä¸€ å‡�</t>
+          <t>L568: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢Subscribe to . Our Musical Friend," or</t>
+          <t>L285: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •information to be had on applying at the complaints, or from whom genuine European , ALICE Tell</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L361: isolated marker/symbol line :: 4</t>
+          <t>L221: isolated marker/symbol line :: J</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1051,13 +1055,13 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: _â€” ______________- ----------------â€” The treatment they adopt is the result of</t>
+          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L311: line starts with punctuation glued to text :: .the experience of one nation, but consists of</t>
+          <t>L285: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •information to be had on applying at the complaints, or from whom genuine European , ALICE Tell</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1103,36 +1107,36 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SLiGHT (odd internal casing), cOLD (odd internal casing) :: SLiGHT cOLD "â€” If rt y = p</t>
+          <t>L695: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: quote/punctuation debris :: unto the third and fourth generation ; indeed, â€”., 171.</t>
+          <t>L289: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD • of -----</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L421: isolated marker/symbol line :: m</t>
+          <t>L359: isolated marker/symbol line :: b.</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L390: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
+          <t>L246: punctuation artifact: repeated periods :: VALLA..............DR. AMOS &amp; SON takes pleasure in rilla is to purify and regenerate thisvitalfluid,</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
       <c r="S8" s="1" t="inlineStr">
         <is>
-          <t>L474: line starts with punctuation glued to text :: ** Sold at the Manufactory of Professor</t>
+          <t>L292: line starts with punctuation glued to text :: _________________________— — correct detail of their cases witha remit-</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr"/>
@@ -1178,19 +1182,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L561: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: â‰¥</t>
+          <t>L810: stray/suspicious non-ASCII glyph(s): U+4E91 CJK UNIFIED IDEOGRAPH-4E91 | isolated marker/symbol line :: 云</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: it seems to be the rod of Him who says, â€¢â€¢ I Both the Ointment and Pills should be</t>
+          <t>L390: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L440: isolated marker/symbol line :: .</t>
+          <t>L360: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1201,13 +1205,13 @@
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L246: punctuation artifact: repeated periods :: VALLA..............DR. AMOS &amp; SON takes pleasure in rilla is to purify and regenerate thisvitalfluid,</t>
+          <t>L268: punctuation artifact: repeated periods :: Head Office....Church Street, Toronto: Persons wishing the above usefulinstru-</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L551: line starts with punctuation glued to text :: .ROBE</t>
+          <t>L311: line starts with punctuation glued to text :: .the experience of one nation, but consists of</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1225,12 +1229,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1253,19 +1257,19 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L615: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: system subject to a return of the dianseâ€”</t>
+          <t>L942: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: For Blackwoodâ€™s Magazine, -------</t>
+          <t>L398: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • YS</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L499: symbol-only separator/garbage line :: 1851.</t>
+          <t>L361: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1276,13 +1280,13 @@
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>L268: punctuation artifact: repeated periods :: Head Office....Church Street, Toronto: Persons wishing the above usefulinstru-</t>
+          <t>L289: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD • of -----</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>L591: line starts with punctuation glued to text :: .Dysentery. Dropsy</t>
+          <t>L398: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • YS</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr"/>
@@ -1305,7 +1309,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1328,19 +1332,19 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L633: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mercurial Diseases â€” Never fd. to</t>
+          <t>L960: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________â€” ------------- ----: ---107 Nassau St., New York.</t>
+          <t>L443: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: known in the world for the•</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L561: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: â‰¥</t>
+          <t>L421: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1351,13 +1355,13 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD â€¢ of -----</t>
+          <t>L329: punctuation artifact: repeated periods :: From the time I first discovered its dropp ng..</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>L599: line starts with digit/letter garbage token | suspicious token(s): 1Morbus (letter/digit mix) :: 1Morbus, I give it to you at the request of Mr Bradford</t>
+          <t>L474: line starts with punctuation glued to text :: ** Sold at the Manufactory of Professor</t>
         </is>
       </c>
       <c r="T11" s="1" t="inlineStr"/>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1403,19 +1407,19 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L692: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): consuMpTives (odd internal casing) :: To consuMpTives â€“ The advertiser</t>
+          <t>L1050: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L202: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: or cash, at Bruceâ€™s New York Type Foundry.</t>
+          <t>L506: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Hair Restorative’ which he liked very much</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L562: isolated marker/symbol line :: o</t>
+          <t>L440: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1426,13 +1430,13 @@
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L329: punctuation artifact: repeated periods :: From the time I first discovered its dropp ng..</t>
+          <t>L367: punctuation artifact: double/multiple hyphen :: Such a medicine we supply in - -----——</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L644: line starts with punctuation glued to text :: .tifiestesin my pos</t>
+          <t>L506: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Hair Restorative’ which he liked very much</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1478,36 +1482,36 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: remÃ©dy all inquirers: moreover, I shall</t>
+          <t>L1246: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00, U+51CF CJK UNIFIED IDEOGRAPH-51CF :: 一 减</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: taining it. will be allowed his bill, at the time â€” New York,</t>
+          <t>L601: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: €holers Infantum You can sell a great deal of your Hair Resto-</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L577: isolated marker/symbol line :: o</t>
+          <t>L499: symbol-only separator/garbage line :: 1851.</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Such a medicine we supply in - -----â€”â€”</t>
+          <t>L517: punctuation artifact: repeated periods :: ing the larger sizes..</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr">
         <is>
-          <t>L842: line starts with punctuation glued to text :: .w high all express in ly. if neglected, end which have now stood the test of public exp-</t>
+          <t>L551: line starts with punctuation glued to text :: .ROBE</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1530,7 +1534,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1553,19 +1557,19 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L942: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ï¼�</t>
+          <t>L1449: stray/suspicious non-ASCII glyph(s): U+2265 GREATER-THAN OR EQUAL TO | isolated marker/symbol line :: ≥</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: GEORGE BRUCE. 8 oâ€™clock in the morning, until 9 at night in</t>
+          <t>L649: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: dividual taking it•</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L625: isolated marker/symbol line :: 3</t>
+          <t>L561: stray/suspicious non-ASCII glyph(s): U+2265 GREATER-THAN OR EQUAL TO | isolated marker/symbol line :: ≥</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1576,13 +1580,13 @@
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L517: punctuation artifact: repeated periods :: ing the larger sizes..</t>
+          <t>L671: punctuation artifact: repeated periods :: [Medicine .. It will press the obligations I am under for the entire</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr">
         <is>
-          <t>L1124: line starts with digit/letter garbage token | suspicious token(s): 1Wholesale (letter/digit mix) :: 1Wholesale and for Exportation by the</t>
+          <t>L591: line starts with punctuation glued to text :: .Dysentery. Dropsy</t>
         </is>
       </c>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1628,34 +1632,38 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L1138: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN :: States it wÃ¤re rapidly becoming gray but up</t>
+          <t>L1457: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: _â€” ______________- ----------------â€” The treatment they adopt is the result of</t>
+          <t>L652: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gently on the Bowel- ©</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L654: isolated marker/symbol line :: u</t>
+          <t>L562: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L854: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L854: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L671: punctuation artifact: repeated periods :: [Medicine .. It will press the obligations I am under for the entire</t>
+          <t>L719: punctuation artifact: repeated periods :: Solicitor.........- Angus Morrison, Esq.</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>L599: line starts with digit/letter garbage token | suspicious token(s): 1Morbus (letter/digit mix) :: 1Morbus, I give it to you at the request of Mr Bradford</t>
+        </is>
+      </c>
       <c r="T15" s="1" t="inlineStr"/>
       <c r="U15" s="1" t="inlineStr"/>
       <c r="V15" s="1" t="inlineStr"/>
@@ -1685,7 +1693,7 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): A1001 (letter/digit mix) :: â€” A1001</t>
+          <t>L364: suspicious token(s): A1001 (letter/digit mix) :: — A1001</t>
         </is>
       </c>
       <c r="I16" s="1" t="inlineStr">
@@ -1695,19 +1703,19 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L1198: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: Head Office...â€¦. Church Street. Toronto:</t>
+          <t>L1604: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CAN ADA upwards of 30 yearsâ€™ extensive and and sue</t>
+          <t>L673: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN :: ™ thousands can about the time of my arrival in the United</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L676: isolated marker/symbol line :: M</t>
+          <t>L568: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1718,11 +1726,15 @@
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L719: punctuation artifact: repeated periods :: Solicitor.........- Angus Morrison, Esq.</t>
+          <t>L721: punctuation artifact: repeated periods :: Bankers.............BANK UP. CANADA</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
-      <c r="S16" s="1" t="inlineStr"/>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>L644: line starts with punctuation glued to text :: .tifiestesin my pos</t>
+        </is>
+      </c>
       <c r="T16" s="1" t="inlineStr"/>
       <c r="U16" s="1" t="inlineStr"/>
       <c r="V16" s="1" t="inlineStr"/>
@@ -1762,19 +1774,19 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L1231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): A1001 (letter/digit mix) :: â€” A1001</t>
+          <t>L1729: stray/suspicious non-ASCII glyph(s): U+4E91 CJK UNIFIED IDEOGRAPH-4E91 | isolated marker/symbol line :: 云</t>
         </is>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tedâ€” inst loss or damage - A CURE WARRANTED- for their use in the following co maiserder</t>
+          <t>L700: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: • • Sold at the Manufactories of Professor</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L695: isolated marker/symbol line :: æ°”</t>
+          <t>L577: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1785,11 +1797,15 @@
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L721: punctuation artifact: repeated periods :: Bankers.............BANK UP. CANADA</t>
+          <t>L734: punctuation artifact: double/multiple hyphen :: e ------------------------ - - cures and directions</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>L842: line starts with punctuation glued to text :: .w high all express in ly. if neglected, end which have now stood the test of public exp-</t>
+        </is>
+      </c>
       <c r="T17" s="1" t="inlineStr"/>
       <c r="U17" s="1" t="inlineStr"/>
       <c r="V17" s="1" t="inlineStr"/>
@@ -1815,21 +1831,17 @@
           <t>L558: suspicious token(s): TUxons (odd internal casing) :: BLOTCHES, BLAINS and Bouts, TUxons, TETTER</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L1246: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ä¸€ å‡�</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L285: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢information to be had on applying at the complaints, or from whom genuine European , ALICE Tell</t>
+          <t>L706: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: are so composed that disease within the range ©-</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L697: isolated marker/symbol line :: p</t>
+          <t>L625: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1840,11 +1852,15 @@
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>L734: punctuation artifact: double/multiple hyphen :: e ------------------------ - - cures and directions</t>
+          <t>L840: punctuation artifact: double/multiple hyphen | suspicious token(s): Filma63 (letter/digit mix) :: -toneused the Filma63--a</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>L1124: line starts with digit/letter garbage token | suspicious token(s): 1Wholesale (letter/digit mix) :: 1Wholesale and for Exportation by the</t>
+        </is>
+      </c>
       <c r="T18" s="1" t="inlineStr"/>
       <c r="U18" s="1" t="inlineStr"/>
       <c r="V18" s="1" t="inlineStr"/>
@@ -1862,7 +1878,7 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SLiGHT (odd internal casing), cOLD (odd internal casing) :: SLiGHT cOLD "â€” If rt y = p</t>
+          <t>L441: suspicious token(s): SLiGHT (odd internal casing), cOLD (odd internal casing) :: SLiGHT cOLD "— If rt y = p</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
@@ -1870,21 +1886,17 @@
           <t>L571: suspicious token(s): FemsleComplaints (odd internal casing) :: FemsleComplaints</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L1317: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SLiGHT (odd internal casing), cOLD (odd internal casing) :: SLiGHT cOLD "â€” If rt y = p</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD â€¢ of -----</t>
+          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L698: isolated marker/symbol line :: 1</t>
+          <t>L654: isolated marker/symbol line :: u</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1895,7 +1907,7 @@
       <c r="P19" s="1" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>L840: punctuation artifact: double/multiple hyphen | suspicious token(s): Filma63 (letter/digit mix) :: -toneused the Filma63--a</t>
+          <t>L912: punctuation artifact: repeated periods | missing space around punctuation :: .-.... teething, by softening the gums,reducing</t>
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr"/>
@@ -1925,21 +1937,17 @@
           <t>L589: suspicious token(s): 2Cholera (letter/digit mix) :: for scrofula is a degeneration of the blood. The a nthl-at 2Cholera</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L1449: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: â‰¥</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: _________________________â€” â€” correct detail of their cases witha remit-</t>
+          <t>L854: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L711: isolated marker/symbol line :: N</t>
+          <t>L676: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -1950,7 +1958,7 @@
       <c r="P20" s="1" t="inlineStr"/>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L912: punctuation artifact: repeated periods | missing space around punctuation :: .-.... teething, by softening the gums,reducing</t>
+          <t>L916: punctuation artifact: repeated periods | suspicious token(s): theirSAUCE (odd internal casing) :: theirSAUCE is, LATE THE BOWELS..</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -1980,21 +1988,17 @@
           <t>L599: line starts with digit/letter garbage token | suspicious token(s): 1Morbus (letter/digit mix) :: 1Morbus, I give it to you at the request of Mr Bradford</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L1508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: system subject to a return of the dianseâ€”</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: every countryâ€”a record, the like</t>
+          <t>L886: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: use. When once tried, its superiority over €</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L719: isolated marker/symbol line :: 10</t>
+          <t>L695: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -2005,7 +2009,7 @@
       <c r="P21" s="1" t="inlineStr"/>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>L916: punctuation artifact: repeated periods | suspicious token(s): theirSAUCE (odd internal casing) :: theirSAUCE is, LATE THE BOWELS..</t>
+          <t>L934: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: well know that diffe- •</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
@@ -2032,24 +2036,20 @@
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>L675: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): HalfRestorative (odd internal casing) :: minutes, if two or on the application ofâ€˜ourâ€™ HalfRestorativeâ€�</t>
-        </is>
-      </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L1527: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mercurial Diseases â€” Never fd. to</t>
-        </is>
-      </c>
+          <t>L675: suspicious token(s): HalfRestorative (odd internal casing) :: minutes, if two or on the application of‘our’ HalfRestorative”</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>L354: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: cimatest. Suman family has its origin directly don.â€� are discernable as a Water mark in</t>
+          <t>L929: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DR. J. €. AVER &amp; Co.</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L770: isolated marker/symbol line :: .</t>
+          <t>L697: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -2060,7 +2060,7 @@
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: hyphen/bullet debris :: â€” â€” -**. DYSPEPSIA â€”No person with this distress-</t>
+          <t>L966: punctuation artifact: hyphen/bullet debris :: — — -**. DYSPEPSIA —No person with this distress-</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -2090,21 +2090,17 @@
           <t>L746: suspicious token(s): WThere (odd internal casing) :: WThere is considerable saving by taking</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L1598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): consuMpTives (odd internal casing) :: To consuMpTives â€“ The advertiser</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Such a medicine we supply in - -----â€”â€”</t>
+          <t>L934: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: well know that diffe- •</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L778: isolated marker/symbol line :: S</t>
+          <t>L698: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -2148,14 +2144,14 @@
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: AYERâ€™S</t>
+          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with © Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L779: isolated marker/symbol line :: 1</t>
+          <t>L711: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2199,14 +2195,14 @@
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>L390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1345: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L781: isolated marker/symbol line :: 0</t>
+          <t>L719: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2248,16 +2244,12 @@
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L398: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ YS</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L794: isolated marker/symbol line :: "</t>
+          <t>L770: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2299,16 +2291,12 @@
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L424: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: it from the patientâ€™s system,</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L828: isolated marker/symbol line :: 103</t>
+          <t>L778: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2319,7 +2307,7 @@
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” anxious to make known to his fellow-suf- _______â€” ......</t>
+          <t>L1204: punctuation artifact: repeated periods :: — anxious to make known to his fellow-suf- _______— ......</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2346,20 +2334,16 @@
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with Â© Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
+          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with © Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Hollowayâ€™s Pills are the best remedy</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L857: isolated marker/symbol line :: P.</t>
+          <t>L779: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2397,16 +2381,12 @@
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L443: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: known in the world for theâ€¢</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L1056: isolated marker/symbol line :: P</t>
+          <t>L781: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2444,16 +2424,12 @@
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN :: â€¢ Hair Restorativeâ€™ which he liked very much</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L1059: isolated marker/symbol line :: 000</t>
+          <t>L794: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2491,16 +2467,12 @@
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L556: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and SKIN DISEASES, Sr. ANTHONYâ€™S FIRE,</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L1079: isolated marker/symbol line :: J</t>
+          <t>L810: stray/suspicious non-ASCII glyph(s): U+4E91 CJK UNIFIED IDEOGRAPH-4E91 | isolated marker/symbol line :: 云</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2538,21 +2510,17 @@
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Fever &amp; Ague.â€”</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L1110: isolated marker/symbol line :: A</t>
+          <t>L828: isolated marker/symbol line :: 103</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L1345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1345: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2576,7 +2544,7 @@
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>L692: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): consuMpTives (odd internal casing) :: To consuMpTives â€“ The advertiser</t>
+          <t>L692: suspicious token(s): consuMpTives (odd internal casing) :: To consuMpTives – The advertiser</t>
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr">
@@ -2585,16 +2553,12 @@
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: â‚¬holers Infantum You can sell a great deal of your Hair Resto-</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L1226: isolated marker/symbol line :: b.</t>
+          <t>L857: isolated marker/symbol line :: P.</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -2632,16 +2596,12 @@
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L607: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: in ** impurity of the bloodâ€� is founded m</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L1227: isolated marker/symbol line :: A</t>
+          <t>L942: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -2675,20 +2635,16 @@
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SEALdo (odd internal casing) :: U PALE SEALdo.â€” 25 barrels very fine,</t>
+          <t>L1292: suspicious token(s): SEALdo (odd internal casing) :: U PALE SEALdo.— 25 barrels very fine,</t>
         </is>
       </c>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: F CAUTION â€” None are genuine unless</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L1228: isolated marker/symbol line :: 4</t>
+          <t>L960: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -2726,16 +2682,12 @@
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ayerâ€™s Cathartic Pills, dose must be</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L1295: isolated marker/symbol line :: m</t>
+          <t>L1050: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -2769,16 +2721,12 @@
       </c>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L649: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: dividual taking itâ€¢</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L1316: isolated marker/symbol line :: .</t>
+          <t>L1056: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
@@ -2812,16 +2760,12 @@
       </c>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L652: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gently on the Bowel- Â©</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L1325: isolated marker/symbol line :: b</t>
+          <t>L1059: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -2855,16 +2799,12 @@
       </c>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: â„¢ thousands can about the time of my arrival in the United</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L1382: symbol-only separator/garbage line :: 1851.</t>
+          <t>L1079: isolated marker/symbol line :: J</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2894,16 +2834,12 @@
       </c>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L675: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): HalfRestorative (odd internal casing) :: minutes, if two or on the application ofâ€˜ourâ€™ HalfRestorativeâ€�</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L1449: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: â‰¥</t>
+          <t>L1110: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2933,16 +2869,12 @@
       </c>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L700: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢ Sold at the Manufactories of Professor</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L1450: isolated marker/symbol line :: o</t>
+          <t>L1226: isolated marker/symbol line :: b.</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2972,16 +2904,12 @@
       </c>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L706: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: are so composed that disease within the range Â©-</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L1464: isolated marker/symbol line :: 00</t>
+          <t>L1227: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -3011,16 +2939,12 @@
       </c>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L750: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N B â€” Directions for the guidance of pa-</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L1466: isolated marker/symbol line :: o</t>
+          <t>L1228: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -3050,16 +2974,12 @@
       </c>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L1517: isolated marker/symbol line :: 3</t>
+          <t>L1295: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -3089,16 +3009,12 @@
       </c>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L793: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: MOFFATâ€™S</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L1552: isolated marker/symbol line :: u</t>
+          <t>L1316: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -3128,16 +3044,12 @@
       </c>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: KEATINGâ€™S</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L1579: isolated marker/symbol line :: M</t>
+          <t>L1325: isolated marker/symbol line :: b</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -3167,16 +3079,12 @@
       </c>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: I creasing demand / ness. Pain and Sore and other constitutic naâ€˜ derangements. The</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L1596: isolated marker/symbol line :: p</t>
+          <t>L1382: symbol-only separator/garbage line :: 1851.</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -3206,16 +3114,12 @@
       </c>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L854: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L1604: isolated marker/symbol line :: æ°”</t>
+          <t>L1449: stray/suspicious non-ASCII glyph(s): U+2265 GREATER-THAN OR EQUAL TO | isolated marker/symbol line :: ≥</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -3245,16 +3149,12 @@
       </c>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Complaints.â€”la the south and west, where</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L1605: isolated marker/symbol line :: 1</t>
+          <t>L1450: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -3284,16 +3184,12 @@
       </c>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L886: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: use. When once tried, its superiority over â‚¬</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L1616: isolated marker/symbol line :: n</t>
+          <t>L1457: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -3323,16 +3219,12 @@
       </c>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tell LEA &amp; all inflammationâ€”will allay ALL PAIN and</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L1617: isolated marker/symbol line :: N</t>
+          <t>L1464: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3362,16 +3254,12 @@
       </c>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L929: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: DR. J. â‚¬. AVER &amp; Co.</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L1625: isolated marker/symbol line :: 10</t>
+          <t>L1466: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3401,16 +3289,12 @@
       </c>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L934: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: well know that diffe- â€¢</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L1686: isolated marker/symbol line :: .</t>
+          <t>L1517: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3440,16 +3324,12 @@
       </c>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L939: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The Family Ca E Children or Adults, mist &amp;c. No. 19. St. Paulâ€™s Church Yard,</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L1694: isolated marker/symbol line :: 1</t>
+          <t>L1552: isolated marker/symbol line :: u</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -3479,16 +3359,12 @@
       </c>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with Â© Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L1697: isolated marker/symbol line :: 0</t>
+          <t>L1579: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -3518,16 +3394,12 @@
       </c>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L942: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: well established fact, and many diseases to N. B â€”To prevent spurious imitations</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L1703: isolated marker/symbol line :: S</t>
+          <t>L1596: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -3557,16 +3429,12 @@
       </c>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L944: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: been compounded which Beth isheir, please observe that the words, KEATINGâ€™S</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L1710: isolated marker/symbol line :: "</t>
+          <t>L1604: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -3596,16 +3464,12 @@
       </c>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: hyphen/bullet debris :: â€” â€” -**. DYSPEPSIA â€”No person with this distress-</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L1747: isolated marker/symbol line :: 103</t>
+          <t>L1605: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3630,21 +3494,17 @@
       <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>L1231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): A1001 (letter/digit mix) :: â€” A1001</t>
+          <t>L1231: suspicious token(s): A1001 (letter/digit mix) :: — A1001</t>
         </is>
       </c>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L982: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” WORCESTERSHIRE SAUCE," the la-</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L1774: isolated marker/symbol line :: B</t>
+          <t>L1616: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3674,16 +3534,12 @@
       </c>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L993: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ladiesâ€™</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L1775: isolated marker/symbol line :: B</t>
+          <t>L1617: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3713,14 +3569,14 @@
       </c>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: system subject to a return of the diseaseâ€”</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
-      <c r="N61" s="1" t="inlineStr"/>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>L1625: isolated marker/symbol line :: 10</t>
+        </is>
+      </c>
       <c r="O61" s="1" t="inlineStr"/>
       <c r="P61" s="1" t="inlineStr"/>
       <c r="Q61" s="1" t="inlineStr"/>
@@ -3743,19 +3599,19 @@
       <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>L1317: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SLiGHT (odd internal casing), cOLD (odd internal casing) :: SLiGHT cOLD "â€” If rt y = p</t>
+          <t>L1317: suspicious token(s): SLiGHT (odd internal casing), cOLD (odd internal casing) :: SLiGHT cOLD "— If rt y = p</t>
         </is>
       </c>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1008: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a cure by these medicines is permanent.â€”</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
-      <c r="N62" s="1" t="inlineStr"/>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>L1686: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
       <c r="O62" s="1" t="inlineStr"/>
       <c r="P62" s="1" t="inlineStr"/>
       <c r="Q62" s="1" t="inlineStr"/>
@@ -3783,14 +3639,14 @@
       </c>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1011: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MERCURAL DISEASES â€”Never fails to era-</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
-      <c r="N63" s="1" t="inlineStr"/>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t>L1694: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="O63" s="1" t="inlineStr"/>
       <c r="P63" s="1" t="inlineStr"/>
       <c r="Q63" s="1" t="inlineStr"/>
@@ -3818,14 +3674,14 @@
       </c>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of Keelingâ€™s Cough Lozenges is re-</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
-      <c r="N64" s="1" t="inlineStr"/>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t>L1697: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O64" s="1" t="inlineStr"/>
       <c r="P64" s="1" t="inlineStr"/>
       <c r="Q64" s="1" t="inlineStr"/>
@@ -3853,14 +3709,14 @@
       </c>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1041: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: No. I Gibâ€™</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
-      <c r="N65" s="1" t="inlineStr"/>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t>L1703: isolated marker/symbol line :: S</t>
+        </is>
+      </c>
       <c r="O65" s="1" t="inlineStr"/>
       <c r="P65" s="1" t="inlineStr"/>
       <c r="Q65" s="1" t="inlineStr"/>
@@ -3888,14 +3744,14 @@
       </c>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1092: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SIR.â€”Thevery excellent properties of your</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
-      <c r="N66" s="1" t="inlineStr"/>
+      <c r="N66" s="1" t="inlineStr">
+        <is>
+          <t>L1710: isolated marker/symbol line :: "</t>
+        </is>
+      </c>
       <c r="O66" s="1" t="inlineStr"/>
       <c r="P66" s="1" t="inlineStr"/>
       <c r="Q66" s="1" t="inlineStr"/>
@@ -3923,14 +3779,14 @@
       </c>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1099: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Palpitation of the Heart, Painterâ€™s Cholic.</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t>L1729: stray/suspicious non-ASCII glyph(s): U+4E91 CJK UNIFIED IDEOGRAPH-4E91 | isolated marker/symbol line :: 云</t>
+        </is>
+      </c>
       <c r="O67" s="1" t="inlineStr"/>
       <c r="P67" s="1" t="inlineStr"/>
       <c r="Q67" s="1" t="inlineStr"/>
@@ -3958,14 +3814,14 @@
       </c>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PILES â€”The original Proprietor of these</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
-      <c r="N68" s="1" t="inlineStr"/>
+      <c r="N68" s="1" t="inlineStr">
+        <is>
+          <t>L1747: isolated marker/symbol line :: 103</t>
+        </is>
+      </c>
       <c r="O68" s="1" t="inlineStr"/>
       <c r="P68" s="1" t="inlineStr"/>
       <c r="Q68" s="1" t="inlineStr"/>
@@ -3993,14 +3849,14 @@
       </c>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L1116: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: yoursâ€”even one of them will check the most</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
-      <c r="N69" s="1" t="inlineStr"/>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t>L1774: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
       <c r="O69" s="1" t="inlineStr"/>
       <c r="P69" s="1" t="inlineStr"/>
       <c r="Q69" s="1" t="inlineStr"/>
@@ -4028,14 +3884,14 @@
       </c>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L1148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TO CONSUMPTIVES â€” The advertiser</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
-      <c r="N70" s="1" t="inlineStr"/>
+      <c r="N70" s="1" t="inlineStr">
+        <is>
+          <t>L1775: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
       <c r="O70" s="1" t="inlineStr"/>
       <c r="P70" s="1" t="inlineStr"/>
       <c r="Q70" s="1" t="inlineStr"/>
@@ -4063,11 +3919,7 @@
       </c>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” anxious to make known to his fellow-suf- _______â€” ......</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr"/>
@@ -4098,11 +3950,7 @@
       </c>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L1291: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ASPE COD OILâ€”100 bbls. Ex. Choice.</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr"/>
@@ -4133,11 +3981,7 @@
       </c>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SEALdo (odd internal casing) :: U PALE SEALdo.â€” 25 barrels very fine,</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr"/>
@@ -4168,11 +4012,7 @@
       </c>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L1310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lug child and the relief will be SUREâ€”yes.</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr"/>
@@ -4203,11 +4043,7 @@
       </c>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L1311: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ABSOLUTELY SUREâ€”to follow the use of</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr"/>
@@ -4233,16 +4069,12 @@
       <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>L1598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): consuMpTives (odd internal casing) :: To consuMpTives â€“ The advertiser</t>
+          <t>L1598: suspicious token(s): consuMpTives (odd internal casing) :: To consuMpTives – The advertiser</t>
         </is>
       </c>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L1329: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Nâ€œ Scottsâ€� Brand, Choice,</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr"/>
@@ -4273,11 +4105,7 @@
       </c>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L1334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GENERAL ASSORTMENT.â€”For Sale</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr"/>
@@ -4308,11 +4136,7 @@
       </c>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L1340: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DVASS,â€”</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr"/>
@@ -4343,11 +4167,7 @@
       </c>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L1345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr"/>
